--- a/output/pdf_financials_xlsx/HWY.xlsx
+++ b/output/pdf_financials_xlsx/HWY.xlsx
@@ -469,15 +469,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -486,15 +482,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -503,15 +495,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -520,15 +508,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.392896</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.370196</v>
       </c>
     </row>
     <row r="8">
@@ -537,15 +521,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -554,15 +534,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -571,15 +547,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>-0.468935</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-0.972366</v>
       </c>
     </row>
     <row r="11">
@@ -588,15 +560,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0.468935</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.972366</v>
       </c>
     </row>
     <row r="12">
@@ -605,15 +573,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -622,15 +586,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -639,15 +599,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -656,15 +612,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-0.005324</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.005003</v>
       </c>
     </row>
     <row r="16">
@@ -673,15 +625,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.492769</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.967363</v>
       </c>
     </row>
     <row r="17">
@@ -690,15 +638,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -741,15 +685,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.492769</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.967363</v>
       </c>
     </row>
     <row r="21">
@@ -758,15 +698,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -775,15 +711,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -818,15 +750,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="26">
@@ -840,10 +768,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>32.245433</v>
       </c>
     </row>
     <row r="27">
@@ -852,15 +778,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.492769</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.967363</v>
       </c>
     </row>
     <row r="28">
@@ -869,15 +791,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -886,15 +804,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.492769</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.967363</v>
       </c>
     </row>
     <row r="30">
@@ -920,15 +834,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -961,15 +871,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -978,15 +884,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -995,15 +897,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1012,15 +910,11 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1029,15 +923,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1046,15 +936,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1063,15 +949,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1093,15 +975,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1110,15 +988,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1127,15 +1001,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1144,15 +1014,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1161,15 +1027,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1178,15 +1040,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1195,15 +1053,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.161278</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.127066</v>
       </c>
     </row>
     <row r="49">
@@ -1212,15 +1066,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.173148</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.143276</v>
       </c>
     </row>
     <row r="50">
@@ -1229,15 +1079,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1246,15 +1092,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1263,15 +1105,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1280,15 +1118,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1297,15 +1131,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1331,15 +1161,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1348,15 +1174,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1365,15 +1187,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>3.426326</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3.872186</v>
       </c>
     </row>
     <row r="59">
@@ -1382,15 +1200,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1399,15 +1213,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1416,15 +1226,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.105884</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.102524</v>
       </c>
     </row>
     <row r="62">
@@ -1433,15 +1239,11 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>3.53221</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>3.97471</v>
       </c>
     </row>
     <row r="63">
@@ -1450,15 +1252,11 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>3.705358</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>4.117986</v>
       </c>
     </row>
     <row r="64">
@@ -1467,15 +1265,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1484,15 +1278,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1501,15 +1291,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1.055</v>
       </c>
     </row>
     <row r="67">
@@ -1518,15 +1304,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1548,15 +1330,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.314274</v>
       </c>
     </row>
     <row r="70">
@@ -1565,15 +1343,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1582,15 +1356,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.314274</v>
       </c>
     </row>
     <row r="72">
@@ -1599,15 +1369,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1616,15 +1382,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1633,15 +1395,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1650,15 +1408,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1684,15 +1438,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1701,15 +1451,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1718,15 +1464,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1740,10 +1482,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>0.1150427025667663</v>
       </c>
     </row>
     <row r="81">
@@ -1752,15 +1492,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1769,15 +1505,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1786,15 +1518,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1803,15 +1531,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1820,15 +1544,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1867,15 +1587,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>8.346372000000001</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>8.525706</v>
       </c>
     </row>
     <row r="89">
@@ -1884,15 +1600,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1914,15 +1626,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1931,15 +1639,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1948,15 +1652,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1978,15 +1678,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1995,15 +1691,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>2.94973</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>2.731803</v>
       </c>
     </row>
     <row r="97">
@@ -2012,15 +1704,11 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.7960715266918879</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.6633832655089162</v>
       </c>
     </row>
     <row r="98">
@@ -2036,15 +1724,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.492769</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.967363</v>
       </c>
     </row>
     <row r="100">
@@ -2053,15 +1737,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2070,15 +1750,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.019529</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>-0.00434</v>
       </c>
     </row>
     <row r="102">
@@ -2087,15 +1763,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2104,15 +1776,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.000364</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.000792</v>
       </c>
     </row>
     <row r="104">
@@ -2134,15 +1802,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2151,15 +1815,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.017954</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.000677</v>
       </c>
     </row>
     <row r="107">
@@ -2181,15 +1841,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2198,15 +1854,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2215,15 +1867,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2232,15 +1880,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2249,15 +1893,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2266,15 +1906,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2283,15 +1919,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2300,15 +1932,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2317,15 +1945,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2334,15 +1958,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2351,15 +1971,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>-0.305282</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>-0.428529</v>
       </c>
     </row>
     <row r="119">
@@ -2381,15 +1997,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2398,15 +2010,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2415,15 +2023,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2432,15 +2036,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2449,15 +2049,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2466,15 +2062,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2483,15 +2075,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2517,15 +2105,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>-0.012805</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2560,15 +2144,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2577,15 +2157,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.167012</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.03342</v>
       </c>
     </row>
     <row r="133">
@@ -2607,15 +2183,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2624,15 +2196,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.155864</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.130404</v>
       </c>
     </row>
   </sheetData>
@@ -2646,7 +2214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2787,7 +2355,11 @@
           <t>Current total</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>0.173148</v>
       </c>
@@ -2859,7 +2431,11 @@
           <t>Exploration and evaluation assets (Note 4)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>3.426326</v>
       </c>
@@ -2880,15 +2456,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
-        <v>3.705358</v>
+        <v>0.015628</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>4.117986</v>
+        <v>0.016909</v>
       </c>
     </row>
     <row r="10">
@@ -2904,19 +2484,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities $</t>
+          <t>Due to related parties (Note 6)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>OtherPayable</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.015628</v>
+        <v>0.74</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.016909</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="11">
@@ -2927,7 +2507,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2935,12 +2515,18 @@
           <t>Due to related parties (Note 6)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="5" t="n">
-        <v>0.74</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.183</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="12">
@@ -2956,17 +2542,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Due to related parties (Note 6)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Loans payable (Note 6)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.872</v>
+        <v>0.314274</v>
       </c>
     </row>
     <row r="13">
@@ -2982,17 +2572,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Loans payable (Note 6)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.755628</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.314274</v>
+        <v>1.386183</v>
       </c>
     </row>
     <row r="14">
@@ -3003,24 +2595,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Non-current</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Capital stock (Note 5)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.755628</v>
+        <v>8.346372000000001</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>1.386183</v>
+        <v>8.525706</v>
       </c>
     </row>
     <row r="15">
@@ -3036,19 +2628,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Capital stock (Note 5)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
+          <t>Share compensation reserve (Note 5)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" s="5" t="n">
-        <v>8.346372000000001</v>
+        <v>1.489016</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>8.525706</v>
+        <v>2.059118</v>
       </c>
     </row>
     <row r="16">
@@ -3064,15 +2652,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Share compensation reserve (Note 5)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
-        <v>1.489016</v>
+        <v>-6.885658</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2.059118</v>
+        <v>-7.853021</v>
       </c>
     </row>
     <row r="17">
@@ -3088,19 +2680,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Total shareholders' equity</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-6.885658</v>
+        <v>2.94973</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-7.853021</v>
+        <v>2.731803</v>
       </c>
     </row>
     <row r="18">
@@ -3116,47 +2708,47 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Total shareholders' equity</t>
+          <t>Total liabilities and shareholders’ equity $</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2.94973</v>
+        <v>3.705358</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>2.731803</v>
+        <v>4.117986</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ equity $</t>
+          <t>Loss for the year $</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3.705358</v>
+        <v>-0.492769</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>4.117986</v>
+        <v>-0.967363</v>
       </c>
     </row>
     <row r="20">
@@ -3167,20 +2759,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
-        <v>-0.492769</v>
+        <v>0.004138</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.967363</v>
+        <v>0.003579</v>
       </c>
     </row>
     <row r="21">
@@ -3196,19 +2792,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Settlement of flow-through premium liability</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" s="5" t="n">
-        <v>0.004138</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>0.003579</v>
+        <v>-0.000352</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -3224,17 +2818,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Settlement of flow-through premium liability</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" s="5" t="n">
-        <v>-0.000352</v>
-      </c>
-      <c r="F22" t="inlineStr">
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.525867</v>
       </c>
     </row>
     <row r="23">
@@ -3250,21 +2848,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Write-down of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.018862</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0.525867</v>
       </c>
     </row>
     <row r="24">
@@ -3280,17 +2878,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets</t>
+          <t>Unrealized foreign exchange</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="5" t="n">
-        <v>0.018862</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004303</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.008163999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3301,20 +2897,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
-        <v>0.004303</v>
+        <v>0.019529</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-0.008163999999999999</v>
+        <v>-0.00434</v>
       </c>
     </row>
     <row r="26">
@@ -3330,15 +2930,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Receivables</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>0.019529</v>
+        <v>-0.000364</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.00434</v>
+        <v>0.000792</v>
       </c>
     </row>
     <row r="27">
@@ -3354,15 +2958,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
-        <v>-0.000364</v>
+        <v>-0.001211</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.000792</v>
+        <v>0.004225</v>
       </c>
     </row>
     <row r="28">
@@ -3378,19 +2986,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Due to related parties</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>-0.001211</v>
+        <v>0.292</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.004225</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="29">
@@ -3406,15 +3010,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
-        <v>0.292</v>
+        <v>-0.155864</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.315</v>
+        <v>-0.130404</v>
       </c>
     </row>
     <row r="30">
@@ -3425,24 +3033,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Reclamation bonds</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>-0.155864</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>-0.130404</v>
+        <v>0.024789</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -3458,17 +3064,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reclamation bonds</t>
+          <t>Acquisition of equipment</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>0.024789</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002385</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-0.002144</v>
       </c>
     </row>
     <row r="32">
@@ -3484,15 +3088,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Acquisition of equipment</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
-        <v>-0.002385</v>
+        <v>-0.324144</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.002144</v>
+        <v>-0.428529</v>
       </c>
     </row>
     <row r="33">
@@ -3508,15 +3116,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Recovery of exploration and evaluation assets expenditures</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>-0.324144</v>
+        <v>0.008397</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.428529</v>
+        <v>0.031725</v>
       </c>
     </row>
     <row r="34">
@@ -3532,15 +3140,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Recovery of exploration and evaluation assets expenditures</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
-        <v>0.008397</v>
+        <v>-0.293343</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.031725</v>
+        <v>-0.398948</v>
       </c>
     </row>
     <row r="35">
@@ -3551,24 +3163,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>-0.293343</v>
+          <t>Proceeds from loans payable</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.398948</v>
+        <v>0.417756</v>
       </c>
     </row>
     <row r="36">
@@ -3584,7 +3194,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Proceeds from loans payable</t>
+          <t>Repayment of loans payable</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3594,7 +3204,7 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.417756</v>
+        <v>-0.035158</v>
       </c>
     </row>
     <row r="37">
@@ -3610,7 +3220,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Repayment of loans payable</t>
+          <t>Proceeds from warrant exercise</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3620,7 +3230,7 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.035158</v>
+        <v>0.113334</v>
       </c>
     </row>
     <row r="38">
@@ -3636,17 +3246,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Proceeds from warrant exercise</t>
+          <t>Issuance of common shares for cash</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="5" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.113334</v>
       </c>
     </row>
     <row r="39">
@@ -3662,12 +3272,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Issuance of common shares for cash</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
-        <v>0.295</v>
+        <v>-0.012805</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3688,17 +3302,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>-0.012805</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.282195</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.495932</v>
       </c>
     </row>
     <row r="41">
@@ -3714,19 +3330,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Change in cash for the year</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.282195</v>
+        <v>-0.167012</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.495932</v>
+        <v>-0.03342</v>
       </c>
     </row>
     <row r="42">
@@ -3742,15 +3358,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Change in cash for the year</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
-        <v>-0.167012</v>
+        <v>0.3264</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.03342</v>
+        <v>0.159388</v>
       </c>
     </row>
     <row r="43">
@@ -3766,19 +3386,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.3264</v>
+        <v>0.159388</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.159388</v>
+        <v>0.125968</v>
       </c>
     </row>
     <row r="44">
@@ -3789,24 +3409,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shares Stock Reserve Deficit Total</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2018 34,980,819 $ 8,093,677 $ 1,459,516 $</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>0.159388</v>
+        <v>3.160304</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.125968</v>
+        <v>-6.392889</v>
       </c>
     </row>
     <row r="45">
@@ -3822,15 +3438,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2018 34,980,819 $ 8,093,677 $ 1,459,516 $</t>
+          <t>Private placement 1,966,664 265,500 29,500</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>3.160304</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>-6.392889</v>
+        <v>0.295</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -3846,12 +3464,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Private placement 1,966,664 265,500 29,500</t>
+          <t>Share issue costs - (12,805) -</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>0.295</v>
+        <v>-0.012805</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3872,17 +3490,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Share issue costs - (12,805) -</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
-        <v>-0.012805</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.492769</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>-0.492769</v>
       </c>
     </row>
     <row r="48">
@@ -3898,15 +3518,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
+          <t>Balance, December 31, 2019 36,947,483 8,346,372 1,489,016</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>-0.492769</v>
+        <v>2.94973</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.492769</v>
+        <v>-6.885658</v>
       </c>
     </row>
     <row r="49">
@@ -3922,15 +3542,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2019 36,947,483 8,346,372 1,489,016</t>
+          <t>Exercise of warrants 566,665 127,334 (14,000)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>2.94973</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-6.885658</v>
+        <v>0.113334</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3946,12 +3568,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Exercise of warrants 566,665 127,334 (14,000)</t>
+          <t>Shares for exploration and evaluation assets 200,000 52,000 -</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>0.113334</v>
+        <v>0.052</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3972,12 +3594,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Shares for exploration and evaluation assets 200,000 52,000 -</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Stock-based compensation - - 525,867</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
-        <v>0.052</v>
+        <v>0.525867</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3998,16 +3624,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stock-based compensation - - 525,867</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Inferred benefit from non-interest bearing loans - - 58,235</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>0.525867</v>
+        <v>0.058235</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4028,41 +3650,35 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Inferred benefit from non-interest bearing loans - - 58,235</t>
+          <t>Balance, December 31, 2020 37,714,148 $ 8,525,706 $ 2,059,118 $</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>0.058235</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.731803</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-7.853021</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Shares Stock Reserve Deficit Total</t>
-        </is>
-      </c>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 37,714,148 $ 8,525,706 $ 2,059,118 $</t>
+          <t>December 31, 2020 December</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>2.731803</v>
+        <v>0.002019</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-7.853021</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="55">
@@ -4071,18 +3687,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>December 31, 2020 December</t>
+          <t>Accounting and audit (Note 6) $</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>0.002019</v>
+        <v>0.0578</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.055875</v>
       </c>
     </row>
     <row r="56">
@@ -4098,15 +3718,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Accounting and audit (Note 6) $</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
-        <v>0.0578</v>
+        <v>0.004138</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.055875</v>
+        <v>0.003579</v>
       </c>
     </row>
     <row r="57">
@@ -4122,19 +3746,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Bank charges and interest</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>0.004138</v>
+        <v>0.001404</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.003579</v>
+        <v>0.001596</v>
       </c>
     </row>
     <row r="58">
@@ -4150,15 +3770,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bank charges and interest</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Consulting fees (Note 6)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
-        <v>0.001404</v>
+        <v>0.3</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.001596</v>
+        <v>0.30644</v>
       </c>
     </row>
     <row r="59">
@@ -4174,15 +3798,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 6)</t>
+          <t>Stock-based compensation (Note 5, 6)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" s="5" t="n">
-        <v>0.3</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.30644</v>
+        <v>0.525867</v>
       </c>
     </row>
     <row r="60">
@@ -4198,17 +3824,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 5, 6)</t>
+          <t>Investor relations and shareholder information</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E60" s="5" t="n">
+        <v>0.00269</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.525867</v>
+        <v>0.00044</v>
       </c>
     </row>
     <row r="61">
@@ -4224,15 +3848,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Investor relations and shareholder information</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>0.00269</v>
+        <v>0.010007</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.00044</v>
+        <v>0.014813</v>
       </c>
     </row>
     <row r="62">
@@ -4248,15 +3872,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Office and administration</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
-        <v>0.010007</v>
+        <v>0.040076</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.014813</v>
+        <v>0.027685</v>
       </c>
     </row>
     <row r="63">
@@ -4272,15 +3900,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Office and administration</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
-        <v>0.040076</v>
+        <v>0.034939</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.027685</v>
+        <v>0.017989</v>
       </c>
     </row>
     <row r="64">
@@ -4296,15 +3928,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Transfer agent and listing fees</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
-        <v>0.034939</v>
+        <v>0.017881</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.017989</v>
+        <v>0.018082</v>
       </c>
     </row>
     <row r="65">
@@ -4320,15 +3956,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Transfer agent and listing fees</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
-        <v>0.017881</v>
+        <v>-0.468935</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.018082</v>
+        <v>-0.972366</v>
       </c>
     </row>
     <row r="66">
@@ -4344,15 +3984,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
+          <t>Settlement of flow-through premium liability (Note 10)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>-0.468935</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>-0.972366</v>
+        <v>0.000352</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4368,12 +4010,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Settlement of flow-through premium liability (Note 10)</t>
+          <t>Write-down of exploration and evaluation assets (Note 4)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>0.000352</v>
+        <v>-0.018862</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4394,17 +4036,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets (Note 4)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Gain (loss) on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
-        <v>-0.018862</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005324</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.005003</v>
       </c>
     </row>
     <row r="69">
@@ -4420,15 +4064,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gain (loss) on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
-        <v>-0.005324</v>
+        <v>-0.492769</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.005003</v>
+        <v>-0.967363</v>
       </c>
     </row>
     <row r="70">
@@ -4444,19 +4092,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.492769</v>
+        <v>-1e-08</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.967363</v>
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="71">
@@ -4467,47 +4115,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>-1e-08</v>
+        <v>35.589676</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>35.589676</v>
-      </c>
-      <c r="F72" s="5" t="n">
         <v>36.980998</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/HWY.xlsx
+++ b/output/pdf_financials_xlsx/HWY.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/HWY.xlsx
+++ b/output/pdf_financials_xlsx/HWY.xlsx
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.011411</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.016409</v>
       </c>
     </row>
     <row r="10">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.468935</v>
+        <v>0.468935</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-0.972366</v>
+        <v>0.972366</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.468935</v>
+        <v>-0.468935</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.972366</v>
+        <v>-0.972366</v>
       </c>
     </row>
     <row r="12">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.014675</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.01324</v>
       </c>
     </row>
     <row r="54">
@@ -2388,7 +2388,11 @@
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="n">
         <v>0.014675</v>
       </c>
@@ -3754,7 +3758,11 @@
           <t>Bank charges and interest</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.001404</v>
       </c>
@@ -3856,7 +3864,11 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>0.010007</v>
       </c>
@@ -3970,10 +3982,10 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>-0.468935</v>
+        <v>0.468935</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>-0.972366</v>
+        <v>0.972366</v>
       </c>
     </row>
     <row r="66">

--- a/output/pdf_financials_xlsx/HWY.xlsx
+++ b/output/pdf_financials_xlsx/HWY.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.159388</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.125968</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.159388</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.125968</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.161278</v>
+        <v>0.00189</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.127066</v>
+        <v>0.001098</v>
       </c>
     </row>
     <row r="49">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/HWY.xlsx
+++ b/output/pdf_financials_xlsx/HWY.xlsx
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002385</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002144</v>
       </c>
     </row>
     <row r="112">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002385</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002144</v>
       </c>
     </row>
     <row r="135">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.155864</v>
+        <v>-0.158249</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.130404</v>
+        <v>-0.132548</v>
       </c>
     </row>
   </sheetData>
@@ -3076,7 +3076,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-0.002385</v>
       </c>
@@ -3450,7 +3454,11 @@
           <t>Private placement 1,966,664 265,500 29,500</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>0.295</v>
       </c>
